--- a/output/Data and Chart Outputs/elering_gas_daily.xlsx
+++ b/output/Data and Chart Outputs/elering_gas_daily.xlsx
@@ -156,6 +156,7 @@
               <a:defRPr/>
             </a:pPr>
             <a:r>
+              <a:rPr sz="1200" b="1"/>
               <a:t>Estonia net gas flows at Balticconnector and Karksi (Elering) (to Sep/26)</a:t>
             </a:r>
           </a:p>
@@ -332,6 +333,7 @@
               <a:defRPr/>
             </a:pPr>
             <a:r>
+              <a:rPr sz="1200" b="1"/>
               <a:t>Estonia gas consumption (Elering) (to Sep/26)</a:t>
             </a:r>
           </a:p>
@@ -867,7 +869,7 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>2026-10-04 22:48 UTC; 1830 days, 2021-09-30 to 2026-10-03</t>
+          <t>2026-10-28 00:51 UTC; 1854 days, 2021-09-30 to 2026-10-27</t>
         </is>
       </c>
     </row>
@@ -1543,7 +1545,7 @@
         <v>46266</v>
       </c>
       <c r="B62" t="n">
-        <v>-0.4102729999999999</v>
+        <v>-0.398324</v>
       </c>
     </row>
   </sheetData>
@@ -2061,7 +2063,7 @@
         <v>46266</v>
       </c>
       <c r="B62" t="n">
-        <v>0.132049</v>
+        <v>0.12859</v>
       </c>
     </row>
   </sheetData>
@@ -2076,7 +2078,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F1831"/>
+  <dimension ref="A1:F1855"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -30875,10 +30877,10 @@
         <v>46283</v>
       </c>
       <c r="B1816" t="n">
-        <v>-14.281</v>
+        <v>-2.332</v>
       </c>
       <c r="F1816" t="n">
-        <v>4.049</v>
+        <v>0.59</v>
       </c>
     </row>
     <row r="1817">
@@ -31029,10 +31031,10 @@
         <v>46297</v>
       </c>
       <c r="B1830" t="n">
-        <v>-17.248</v>
+        <v>-17.999</v>
       </c>
       <c r="F1830" t="n">
-        <v>5.318</v>
+        <v>5.58</v>
       </c>
     </row>
     <row r="1831">
@@ -31040,10 +31042,274 @@
         <v>46298</v>
       </c>
       <c r="B1831" t="n">
-        <v>-2.979</v>
+        <v>-17.919</v>
       </c>
       <c r="F1831" t="n">
-        <v>0.663</v>
+        <v>4.635</v>
+      </c>
+    </row>
+    <row r="1832">
+      <c r="A1832" s="4" t="n">
+        <v>46299</v>
+      </c>
+      <c r="B1832" t="n">
+        <v>-11.726</v>
+      </c>
+      <c r="F1832" t="n">
+        <v>4.558</v>
+      </c>
+    </row>
+    <row r="1833">
+      <c r="A1833" s="4" t="n">
+        <v>46300</v>
+      </c>
+      <c r="B1833" t="n">
+        <v>-16.289</v>
+      </c>
+      <c r="F1833" t="n">
+        <v>5.974</v>
+      </c>
+    </row>
+    <row r="1834">
+      <c r="A1834" s="4" t="n">
+        <v>46301</v>
+      </c>
+      <c r="B1834" t="n">
+        <v>-16.31</v>
+      </c>
+      <c r="F1834" t="n">
+        <v>5.535</v>
+      </c>
+    </row>
+    <row r="1835">
+      <c r="A1835" s="4" t="n">
+        <v>46302</v>
+      </c>
+      <c r="B1835" t="n">
+        <v>-16.321</v>
+      </c>
+      <c r="F1835" t="n">
+        <v>6.621</v>
+      </c>
+    </row>
+    <row r="1836">
+      <c r="A1836" s="4" t="n">
+        <v>46303</v>
+      </c>
+      <c r="B1836" t="n">
+        <v>-19.684</v>
+      </c>
+      <c r="F1836" t="n">
+        <v>6.467</v>
+      </c>
+    </row>
+    <row r="1837">
+      <c r="A1837" s="4" t="n">
+        <v>46304</v>
+      </c>
+      <c r="B1837" t="n">
+        <v>-19.389</v>
+      </c>
+      <c r="F1837" t="n">
+        <v>6.453</v>
+      </c>
+    </row>
+    <row r="1838">
+      <c r="A1838" s="4" t="n">
+        <v>46305</v>
+      </c>
+      <c r="B1838" t="n">
+        <v>-20.758</v>
+      </c>
+      <c r="F1838" t="n">
+        <v>6.187</v>
+      </c>
+    </row>
+    <row r="1839">
+      <c r="A1839" s="4" t="n">
+        <v>46306</v>
+      </c>
+      <c r="B1839" t="n">
+        <v>-21.664</v>
+      </c>
+      <c r="F1839" t="n">
+        <v>6.142</v>
+      </c>
+    </row>
+    <row r="1840">
+      <c r="A1840" s="4" t="n">
+        <v>46307</v>
+      </c>
+      <c r="B1840" t="n">
+        <v>-25.93</v>
+      </c>
+      <c r="F1840" t="n">
+        <v>5.798</v>
+      </c>
+    </row>
+    <row r="1841">
+      <c r="A1841" s="4" t="n">
+        <v>46308</v>
+      </c>
+      <c r="B1841" t="n">
+        <v>-27.849</v>
+      </c>
+      <c r="F1841" t="n">
+        <v>6.563</v>
+      </c>
+    </row>
+    <row r="1842">
+      <c r="A1842" s="4" t="n">
+        <v>46309</v>
+      </c>
+      <c r="B1842" t="n">
+        <v>-22.556</v>
+      </c>
+      <c r="F1842" t="n">
+        <v>6.908</v>
+      </c>
+    </row>
+    <row r="1843">
+      <c r="A1843" s="4" t="n">
+        <v>46310</v>
+      </c>
+      <c r="B1843" t="n">
+        <v>-22.625</v>
+      </c>
+      <c r="F1843" t="n">
+        <v>6.104</v>
+      </c>
+    </row>
+    <row r="1844">
+      <c r="A1844" s="4" t="n">
+        <v>46311</v>
+      </c>
+      <c r="B1844" t="n">
+        <v>-24.852</v>
+      </c>
+      <c r="F1844" t="n">
+        <v>6.521</v>
+      </c>
+    </row>
+    <row r="1845">
+      <c r="A1845" s="4" t="n">
+        <v>46312</v>
+      </c>
+      <c r="B1845" t="n">
+        <v>-24.882</v>
+      </c>
+      <c r="F1845" t="n">
+        <v>6.077</v>
+      </c>
+    </row>
+    <row r="1846">
+      <c r="A1846" s="4" t="n">
+        <v>46313</v>
+      </c>
+      <c r="B1846" t="n">
+        <v>-25.646</v>
+      </c>
+      <c r="F1846" t="n">
+        <v>7.841</v>
+      </c>
+    </row>
+    <row r="1847">
+      <c r="A1847" s="4" t="n">
+        <v>46314</v>
+      </c>
+      <c r="B1847" t="n">
+        <v>7.502</v>
+      </c>
+      <c r="F1847" t="n">
+        <v>1.285</v>
+      </c>
+    </row>
+    <row r="1848">
+      <c r="A1848" s="4" t="n">
+        <v>46315</v>
+      </c>
+      <c r="B1848" t="n">
+        <v>54.178</v>
+      </c>
+      <c r="F1848" t="n">
+        <v>8.055999999999999</v>
+      </c>
+    </row>
+    <row r="1849">
+      <c r="A1849" s="4" t="n">
+        <v>46316</v>
+      </c>
+      <c r="B1849" t="n">
+        <v>42.688</v>
+      </c>
+      <c r="F1849" t="n">
+        <v>7.766</v>
+      </c>
+    </row>
+    <row r="1850">
+      <c r="A1850" s="4" t="n">
+        <v>46317</v>
+      </c>
+      <c r="B1850" t="n">
+        <v>55.226</v>
+      </c>
+      <c r="F1850" t="n">
+        <v>7.134</v>
+      </c>
+    </row>
+    <row r="1851">
+      <c r="A1851" s="4" t="n">
+        <v>46318</v>
+      </c>
+      <c r="B1851" t="n">
+        <v>56.215</v>
+      </c>
+      <c r="F1851" t="n">
+        <v>6.672</v>
+      </c>
+    </row>
+    <row r="1852">
+      <c r="A1852" s="4" t="n">
+        <v>46319</v>
+      </c>
+      <c r="B1852" t="n">
+        <v>36.751</v>
+      </c>
+      <c r="F1852" t="n">
+        <v>6.193</v>
+      </c>
+    </row>
+    <row r="1853">
+      <c r="A1853" s="4" t="n">
+        <v>46320</v>
+      </c>
+      <c r="B1853" t="n">
+        <v>42.034</v>
+      </c>
+      <c r="F1853" t="n">
+        <v>6.02</v>
+      </c>
+    </row>
+    <row r="1854">
+      <c r="A1854" s="4" t="n">
+        <v>46321</v>
+      </c>
+      <c r="B1854" t="n">
+        <v>7.403</v>
+      </c>
+      <c r="F1854" t="n">
+        <v>6.959</v>
+      </c>
+    </row>
+    <row r="1855">
+      <c r="A1855" s="4" t="n">
+        <v>46322</v>
+      </c>
+      <c r="B1855" t="n">
+        <v>0</v>
+      </c>
+      <c r="F1855" t="n">
+        <v>5.898</v>
       </c>
     </row>
   </sheetData>
